--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.20699344152104</v>
+        <v>6.69613643424717</v>
       </c>
       <c r="D2" t="n">
-        <v>41.38236339311712</v>
+        <v>6.724634051381533</v>
       </c>
       <c r="E2" t="n">
-        <v>6.340615484846087</v>
+        <v>1.030350016287489</v>
       </c>
       <c r="F2" t="n">
-        <v>6.378800029827644</v>
+        <v>1.036555004846992</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.44395080530629</v>
+        <v>6.247142005862272</v>
       </c>
       <c r="D3" t="n">
-        <v>38.4267485065037</v>
+        <v>6.244346632306851</v>
       </c>
       <c r="E3" t="n">
-        <v>6.340615484846087</v>
+        <v>1.030350016287489</v>
       </c>
       <c r="F3" t="n">
-        <v>6.378800029827644</v>
+        <v>1.036555004846992</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.06403236208096</v>
+        <v>4.235405258838156</v>
       </c>
       <c r="D4" t="n">
-        <v>26.05006799556343</v>
+        <v>4.233136049279057</v>
       </c>
       <c r="E4" t="n">
-        <v>6.340615484846087</v>
+        <v>1.030350016287489</v>
       </c>
       <c r="F4" t="n">
-        <v>6.378800029827644</v>
+        <v>1.036555004846992</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.64092227325781</v>
+        <v>6.766649869404394</v>
       </c>
       <c r="D5" t="n">
-        <v>41.65548239637917</v>
+        <v>6.769015889411615</v>
       </c>
       <c r="E5" t="n">
-        <v>6.340615484846087</v>
+        <v>1.030350016287489</v>
       </c>
       <c r="F5" t="n">
-        <v>6.378800029827644</v>
+        <v>1.036555004846992</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
